--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487478_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487478_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4237</v>
+        <v>3.0954</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4808</v>
+        <v>1.8208</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9429</v>
+        <v>1.2746</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4948</v>
@@ -610,13 +610,13 @@
         <v>1.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6063</v>
+        <v>2.278</v>
       </c>
       <c r="T2" t="n">
-        <v>1.061</v>
+        <v>1.4009</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5453</v>
+        <v>0.8771</v>
       </c>
       <c r="V2" t="n">
         <v>0.3329</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6162</v>
+        <v>1.6418</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5363</v>
+        <v>2.3481</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9201</v>
+        <v>-0.7062</v>
       </c>
       <c r="G3" t="n">
         <v>0.6369</v>
@@ -688,13 +688,13 @@
         <v>0.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8007</v>
+        <v>0.8263</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0433</v>
+        <v>0.8551</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2427</v>
+        <v>-0.0288</v>
       </c>
       <c r="V3" t="n">
         <v>1.5495</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. NIETO GONZALEZ</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5535</v>
+        <v>0.6031</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6938</v>
+        <v>0.9072</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1403</v>
+        <v>-0.304</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5324</v>
+        <v>0.3908</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0326</v>
+        <v>-1.2818</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5651</v>
+        <v>1.6726</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1145</v>
+        <v>0.7784</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3014</v>
+        <v>-1.2828</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8131</v>
+        <v>2.0612</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6469</v>
+        <v>-0.3875</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2687</v>
+        <v>0.001</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.3782</v>
+        <v>-0.3886</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3709</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1066</v>
+        <v>0.2123</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7544</v>
+        <v>0.1288</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3522</v>
+        <v>0.0835</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>E. CZERAPOWIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0365</v>
+        <v>0.0291</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4813</v>
+        <v>2.6262</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5179</v>
+        <v>-2.5972</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3908</v>
+        <v>1.6748</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2818</v>
+        <v>0.5747</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6726</v>
+        <v>1.1001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7784</v>
+        <v>5.0717</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2828</v>
+        <v>1.1841</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0612</v>
+        <v>3.8876</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3875</v>
+        <v>-3.3969</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001</v>
+        <v>-0.6093</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3886</v>
+        <v>-2.7875</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.5668</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4273</v>
+        <v>0.3335</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.297</v>
+        <v>0.4923</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1303</v>
+        <v>-0.1588</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2326</v>
+        <v>-0.0617</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9366</v>
+        <v>1.8937</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1692</v>
+        <v>-1.9554</v>
       </c>
       <c r="G6" t="n">
         <v>-1.8069</v>
@@ -922,13 +922,13 @@
         <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.018</v>
+        <v>0.1529</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5264</v>
+        <v>0.4834</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5444</v>
+        <v>-0.3305</v>
       </c>
       <c r="V6" t="n">
         <v>2.3756</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>J. NIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8108</v>
+        <v>-0.2147</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7924</v>
+        <v>2.1127</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0183</v>
+        <v>-2.3275</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1232</v>
+        <v>-0.5324</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2593</v>
+        <v>1.0326</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8639</v>
+        <v>-1.5651</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.269</v>
+        <v>2.1145</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8541</v>
+        <v>1.3014</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5851</v>
+        <v>0.8131</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8542</v>
+        <v>-2.6469</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4052</v>
+        <v>-0.2687</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.449</v>
+        <v>-2.3782</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3332</v>
+        <v>1.3385</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5234</v>
+        <v>1.1733</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8566</v>
+        <v>0.1651</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. CZERAPOWIC</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0885</v>
+        <v>-0.3766</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9364</v>
+        <v>0.0427</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0249</v>
+        <v>-0.4193</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6748</v>
+        <v>-2.1232</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5747</v>
+        <v>-1.2593</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1001</v>
+        <v>-0.8639</v>
       </c>
       <c r="J8" t="n">
-        <v>5.0717</v>
+        <v>-0.269</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1841</v>
+        <v>-0.8541</v>
       </c>
       <c r="L8" t="n">
-        <v>3.8876</v>
+        <v>0.5851</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3969</v>
+        <v>-1.8542</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6093</v>
+        <v>-0.4052</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.7875</v>
+        <v>-1.449</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7841</v>
+        <v>0.7674</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1976</v>
+        <v>0.3117</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5865</v>
+        <v>0.4557</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7772</v>
+        <v>-3.2446</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2932</v>
+        <v>-2.6002</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.484</v>
+        <v>-0.6444</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2229</v>
@@ -1156,13 +1156,13 @@
         <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2671</v>
+        <v>-0.2003</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2664</v>
+        <v>-0.0406</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0007</v>
+        <v>-0.1597</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2754</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.0523</v>
+        <v>-6.6884</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7612</v>
+        <v>-2.7447</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.2912</v>
+        <v>-3.9437</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1786</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5823</v>
+        <v>-0.2183</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3305</v>
+        <v>0.347</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.5653</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3329</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4045</v>
+        <v>-5.2166</v>
       </c>
       <c r="E11" t="n">
-        <v>5.218399999999999</v>
+        <v>6.406499999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.623</v>
+        <v>-11.6231</v>
       </c>
       <c r="G11" t="n">
         <v>-6.6563</v>
@@ -1312,13 +1312,13 @@
         <v>8.8131</v>
       </c>
       <c r="S11" t="n">
-        <v>4.302199999999999</v>
+        <v>5.4903</v>
       </c>
       <c r="T11" t="n">
-        <v>3.964</v>
+        <v>5.151899999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3381000000000002</v>
+        <v>0.3382999999999998</v>
       </c>
       <c r="V11" t="n">
         <v>1.8248</v>
@@ -1327,13 +1327,13 @@
         <v>5.3595</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.5348</v>
+        <v>-3.534799999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.361</v>
+        <v>3.797</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4009</v>
+        <v>3.4094</v>
       </c>
       <c r="F12" t="n">
-        <v>1.96</v>
+        <v>0.3876</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0605</v>
+        <v>5.2073</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6611</v>
+        <v>-0.6781</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6007</v>
+        <v>5.8854</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8897</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2487</v>
+        <v>0.4083</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3589</v>
+        <v>5.5917</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1707</v>
+        <v>-0.7927</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4125</v>
+        <v>-1.0864</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2417</v>
+        <v>0.2937</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3917</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8501</v>
+        <v>0.0401</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2151</v>
+        <v>0.0717</v>
       </c>
       <c r="U12" t="n">
-        <v>1.635</v>
+        <v>-0.0316</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9412</v>
+        <v>-0.2754</v>
       </c>
       <c r="W12" t="n">
         <v>0.2754</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.0687</v>
+        <v>3.6762</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3071</v>
+        <v>2.1593</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2384</v>
+        <v>1.5169</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2073</v>
+        <v>2.041</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6781</v>
+        <v>-0.7833</v>
       </c>
       <c r="I13" t="n">
-        <v>5.8854</v>
+        <v>2.8242</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>1.9525</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4083</v>
+        <v>-0.0375</v>
       </c>
       <c r="L13" t="n">
-        <v>5.5917</v>
+        <v>1.99</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7927</v>
+        <v>0.0885</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0864</v>
+        <v>-0.7458</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2937</v>
+        <v>0.8343</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7626</v>
+        <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6882</v>
+        <v>-0.1689</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0306</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6576</v>
+        <v>-0.1384</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0263</v>
+        <v>3.0015</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1593</v>
+        <v>5.1433</v>
       </c>
       <c r="F14" t="n">
-        <v>0.867</v>
+        <v>-2.1418</v>
       </c>
       <c r="G14" t="n">
-        <v>2.041</v>
+        <v>2.1655</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7833</v>
+        <v>-0.3644</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8242</v>
+        <v>2.5298</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9525</v>
+        <v>4.5696</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0375</v>
+        <v>0.4491</v>
       </c>
       <c r="L14" t="n">
-        <v>1.99</v>
+        <v>4.1205</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0885</v>
+        <v>-2.4041</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7458</v>
+        <v>-0.8135</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8343</v>
+        <v>-1.5906</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8189</v>
+        <v>-0.6145</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0306</v>
+        <v>-0.31</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7883</v>
+        <v>-0.3045</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2166</v>
+        <v>0.8837</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8435</v>
+        <v>2.7144</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3277</v>
+        <v>3.2254</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4842</v>
+        <v>-0.511</v>
       </c>
       <c r="G15" t="n">
         <v>2.1197</v>
@@ -1624,13 +1624,13 @@
         <v>0.5875</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1363</v>
+        <v>0.0072</v>
       </c>
       <c r="T15" t="n">
-        <v>0.207</v>
+        <v>0.1047</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0708</v>
+        <v>-0.0975</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2141</v>
+        <v>2.487</v>
       </c>
       <c r="E16" t="n">
         <v>2.2958</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.1912</v>
       </c>
       <c r="G16" t="n">
         <v>3.8963</v>
@@ -1702,13 +1702,13 @@
         <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6822</v>
+        <v>-0.4093</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0306</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6516</v>
+        <v>-0.3788</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9957</v>
+        <v>1.9285</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3246</v>
+        <v>0.6846</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.329</v>
+        <v>1.2439</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1655</v>
+        <v>1.0605</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3644</v>
+        <v>1.6611</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5298</v>
+        <v>-0.6007</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5696</v>
+        <v>0.8897</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4491</v>
+        <v>1.2487</v>
       </c>
       <c r="L17" t="n">
-        <v>4.1205</v>
+        <v>-0.3589</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4041</v>
+        <v>0.1707</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8135</v>
+        <v>0.4125</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5906</v>
+        <v>-0.2417</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6203</v>
+        <v>1.4176</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1286</v>
+        <v>0.4987</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4916</v>
+        <v>0.9188</v>
       </c>
       <c r="V17" t="n">
+        <v>-0.9412</v>
+      </c>
+      <c r="W17" t="n">
         <v>0.2754</v>
       </c>
-      <c r="W17" t="n">
-        <v>0.8837</v>
-      </c>
       <c r="X17" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9757</v>
+        <v>1.7772</v>
       </c>
       <c r="E18" t="n">
-        <v>1.634</v>
+        <v>0.2128</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6583</v>
+        <v>1.5644</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2106</v>
+        <v>-0.6027</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2903</v>
+        <v>-1.0272</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5009</v>
+        <v>0.4245</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3981</v>
+        <v>-0.0255</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7487</v>
+        <v>-0.2825</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1468</v>
+        <v>0.257</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1875</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5416</v>
+        <v>-0.7447</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6459</v>
+        <v>0.1676</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4101</v>
+        <v>0.0297</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2358</v>
+        <v>-0.0371</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6459</v>
+        <v>0.0668</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6912</v>
+        <v>0.9655</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1966</v>
+        <v>1.327</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8878</v>
+        <v>-0.3615</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6027</v>
+        <v>0.2106</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0272</v>
+        <v>-1.2903</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4245</v>
+        <v>1.5009</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0255</v>
+        <v>1.3981</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2825</v>
+        <v>-0.7487</v>
       </c>
       <c r="L19" t="n">
-        <v>0.257</v>
+        <v>2.1468</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-1.1875</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7447</v>
+        <v>-0.5416</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1676</v>
+        <v>-0.6459</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0563</v>
+        <v>-0.4202</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4464</v>
+        <v>-0.0712</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6099</v>
+        <v>-0.3491</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4785</v>
+        <v>0.6712</v>
       </c>
       <c r="E20" t="n">
         <v>1.0557</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5772</v>
+        <v>-0.3845</v>
       </c>
       <c r="G20" t="n">
         <v>0.6860000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4034</v>
+        <v>-0.2107</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2376</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1658</v>
+        <v>0.0269</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6039</v>
+        <v>-5.4379</v>
       </c>
       <c r="E21" t="n">
         <v>-2.9437</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6602</v>
+        <v>-2.4942</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9243</v>
@@ -2092,13 +2092,13 @@
         <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0505</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3276</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7229</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2166</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6459</v>
+        <v>-6.4469</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7418</v>
+        <v>-4.9465</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9042</v>
+        <v>-1.5004</v>
       </c>
       <c r="G22" t="n">
         <v>-6.2036</v>
@@ -2170,13 +2170,13 @@
         <v>1.3709</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5587</v>
+        <v>-0.3596</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2358</v>
+        <v>0.0312</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7946</v>
+        <v>-0.3908</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2754</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.404900000000002</v>
+        <v>9.133700000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>11.623</v>
+        <v>11.6231</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.218400000000001</v>
+        <v>-2.489400000000001</v>
       </c>
       <c r="G23" t="n">
         <v>6.656299999999998</v>
@@ -2233,7 +2233,7 @@
         <v>-10.5834</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.140000000000001</v>
+        <v>-8.139999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-2.4432</v>
@@ -2248,13 +2248,13 @@
         <v>14.6885</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.302200000000001</v>
+        <v>-1.5732</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3383000000000002</v>
+        <v>-0.3384</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.964</v>
+        <v>-1.2352</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8249</v>
